--- a/record_linkage_groundtruth/industry_RL_groundtruth.xlsx
+++ b/record_linkage_groundtruth/industry_RL_groundtruth.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\OneDrive\Desktop\Uni\Ingegneria Dati\homework5\Record Linkage Groundtruth\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\OneDrive\Desktop\Uni\Ingegneria Dati\homework5\record_linkage_groundtruth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39F2416-5B81-4F1A-9BAB-FEFDC507621F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A944A53-D8FA-490F-A669-316D66075895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,12 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>row_index_1</t>
   </si>
@@ -37,36 +38,12 @@
     <t>is_match</t>
   </si>
   <si>
-    <t>Celon Laboratories</t>
-  </si>
-  <si>
     <t>industryname_1</t>
   </si>
   <si>
     <t>industryname_2</t>
   </si>
   <si>
-    <t>Pharma</t>
-  </si>
-  <si>
-    <t>Huadong Medicine Co. Ltd</t>
-  </si>
-  <si>
-    <t>['Healthcare', 'HealthCare Products', 'Pharmaceutical']</t>
-  </si>
-  <si>
-    <t>Zuora</t>
-  </si>
-  <si>
-    <t>['Technology', 'Software and IT', 'Software Products', 'Software and IT Infrastructure']</t>
-  </si>
-  <si>
-    <t>Rackspace</t>
-  </si>
-  <si>
-    <t>IT Services &amp; Consulting</t>
-  </si>
-  <si>
     <t>Shanghai Tianchen Co. Ltd</t>
   </si>
   <si>
@@ -79,24 +56,12 @@
     <t>['Real Estate', 'Consumer Services', 'Wood Products', 'Property Investments']</t>
   </si>
   <si>
-    <t>U &amp; I TEAM PROPERTIES LTD</t>
-  </si>
-  <si>
     <t>sector_1</t>
   </si>
   <si>
-    <t>68100 - Buying and selling of own real estate</t>
-  </si>
-  <si>
     <t>sector_2</t>
   </si>
   <si>
-    <t>Z D PROPERTY MANAGEMENT LIMITED</t>
-  </si>
-  <si>
-    <t>68209 - Other letting and operating of own or leased real estate</t>
-  </si>
-  <si>
     <t>Wharf (holdings)</t>
   </si>
   <si>
@@ -109,21 +74,9 @@
     <t>['Real Estate', 'Investments', 'Property Investments']</t>
   </si>
   <si>
-    <t>YIT</t>
-  </si>
-  <si>
     <t>Industrials</t>
   </si>
   <si>
-    <t>Heavy construction</t>
-  </si>
-  <si>
-    <t>H &amp; B BUILDERS &amp; DECORATORS LIMITED</t>
-  </si>
-  <si>
-    <t>42990 - Construction of other civil engineering projects not elsewhere classified</t>
-  </si>
-  <si>
     <t>['Industries', 'Engineering Products', 'Engineering Services', 'Construction Materials', 'Construction']</t>
   </si>
   <si>
@@ -148,42 +101,6 @@
     <t>Sales &amp; Marketing</t>
   </si>
   <si>
-    <t>SOL SpA</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Aica Kogyo Company</t>
-  </si>
-  <si>
-    <t>Savita Oil Technologies</t>
-  </si>
-  <si>
-    <t>Chemicals / Agri Inputs</t>
-  </si>
-  <si>
-    <t>Cnnc Hua Yuan Titanium Dioxide Co., Ltd</t>
-  </si>
-  <si>
-    <t>['Basic Materials', 'Chemicals']</t>
-  </si>
-  <si>
-    <t>['Industries', 'Chemicals', 'Construction Materials', 'Conglomerate']</t>
-  </si>
-  <si>
-    <t>KURUMI Real Estate</t>
-  </si>
-  <si>
-    <t>Architecture</t>
-  </si>
-  <si>
-    <t>LivSpace</t>
-  </si>
-  <si>
-    <t>Architecture &amp; Interior Design</t>
-  </si>
-  <si>
     <t>Oak Street Health, Inc.</t>
   </si>
   <si>
@@ -196,19 +113,91 @@
     <t>Healthcare</t>
   </si>
   <si>
-    <t>Alpha Bank</t>
-  </si>
-  <si>
     <t>Financials</t>
   </si>
   <si>
     <t>Banks</t>
   </si>
   <si>
-    <t>M J FINANCES LTD</t>
-  </si>
-  <si>
-    <t>64191 - Banks</t>
+    <t>Erste Bank</t>
+  </si>
+  <si>
+    <t>Dexia</t>
+  </si>
+  <si>
+    <t>Ammerer Bed Company</t>
+  </si>
+  <si>
+    <t>Rancilio</t>
+  </si>
+  <si>
+    <t>Consumer goods</t>
+  </si>
+  <si>
+    <t>Durable household products</t>
+  </si>
+  <si>
+    <t>Saviola Holding Srl</t>
+  </si>
+  <si>
+    <t>Yama Spa</t>
+  </si>
+  <si>
+    <t>Finance, Insurance, and Real Estate</t>
+  </si>
+  <si>
+    <t>Corporation</t>
+  </si>
+  <si>
+    <t>Netcompany</t>
+  </si>
+  <si>
+    <t>Softpedia</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>PUMA</t>
+  </si>
+  <si>
+    <t>Benetton Group</t>
+  </si>
+  <si>
+    <t>Clothing &amp; accessories</t>
+  </si>
+  <si>
+    <t>Luxair</t>
+  </si>
+  <si>
+    <t>Dba</t>
+  </si>
+  <si>
+    <t>Consumer services</t>
+  </si>
+  <si>
+    <t>Airlines</t>
+  </si>
+  <si>
+    <t>Arburg</t>
+  </si>
+  <si>
+    <t>J. Schmalz</t>
+  </si>
+  <si>
+    <t>Industrial machinery</t>
+  </si>
+  <si>
+    <t>Deutsche Post</t>
+  </si>
+  <si>
+    <t>Post Danmark</t>
+  </si>
+  <si>
+    <t>Delivery services</t>
   </si>
 </sst>
 </file>
@@ -278,26 +267,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -600,15 +575,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="11.3515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.17578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.5859375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="68.1171875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="61.05859375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="61.05859375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="61.05859375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="61.05859375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.5">
@@ -625,16 +600,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>22</v>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -642,22 +617,28 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A2">
-        <v>10</v>
+        <v>1583</v>
       </c>
       <c r="B2">
-        <v>24</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -665,22 +646,28 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A3">
-        <v>1795</v>
+        <v>54158</v>
       </c>
       <c r="B3">
-        <v>1818</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>14</v>
+        <v>13343</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>37</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -693,17 +680,17 @@
       <c r="B4">
         <v>138</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>16</v>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -711,22 +698,28 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A5">
-        <v>156</v>
+        <v>49819</v>
       </c>
       <c r="B5">
-        <v>317</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>24</v>
+        <v>40149</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -739,17 +732,17 @@
       <c r="B6">
         <v>370</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>28</v>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -757,25 +750,28 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A7">
-        <v>44406</v>
+        <v>38912</v>
       </c>
       <c r="B7">
-        <v>44411</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>33</v>
+        <v>22849</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -788,17 +784,17 @@
       <c r="B8">
         <v>44560</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>36</v>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -811,17 +807,17 @@
       <c r="B9">
         <v>52135</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>41</v>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -829,22 +825,28 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A10">
-        <v>54464</v>
+        <v>48817</v>
       </c>
       <c r="B10">
-        <v>54479</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>49</v>
+        <v>30005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -852,19 +854,28 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A11">
-        <v>54614</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>48</v>
+        <v>53030</v>
+      </c>
+      <c r="B11">
+        <v>52367</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>52</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -872,22 +883,28 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A12">
-        <v>11234</v>
+        <v>4755</v>
       </c>
       <c r="B12">
-        <v>16857</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>52</v>
+        <v>681</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>53</v>
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" t="s">
+        <v>55</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -901,17 +918,17 @@
       <c r="B13">
         <v>35470</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>57</v>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -919,32 +936,32 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A14">
-        <v>18036</v>
+        <v>43924</v>
       </c>
       <c r="B14">
-        <v>40001</v>
-      </c>
-      <c r="C14" s="10" t="s">
+        <v>34856</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>62</v>
+      <c r="H14" t="s">
+        <v>58</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="C15" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
